--- a/project/20260325_프로젝트계획서.xlsx
+++ b/project/20260325_프로젝트계획서.xlsx
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>개인 프로젝트 계획서</t>
   </si>
@@ -27,9 +27,6 @@
     <t>프로젝트 제목</t>
   </si>
   <si>
-    <t>SNS 프로젝트 (모바일 기반 소셜 네트워크 서비스)</t>
-  </si>
-  <si>
     <t>과정명</t>
   </si>
   <si>
@@ -45,9 +42,6 @@
     <t>발표일</t>
   </si>
   <si>
-    <t>2026-03-25</t>
-  </si>
-  <si>
     <t>담당강사</t>
   </si>
   <si>
@@ -57,10 +51,24 @@
     <t>프로젝트 주제 및 개발목적</t>
   </si>
   <si>
-    <t xml:space="preserve"> - SNS 프로젝트의 주제는 모바일 퍼스트 소셜 네트워크 서비스입니다. 인스타그램, 트위터 등 현대의 소셜 미디어에서 자주 사용되는 핵심 기능(피드, 스토리, 실시간 채팅, 지도 기반 장소 공유 등)을 Next.js와 Firebase를 활용하여 직접 구현하였습니다. 단순 기능 구현에 그치지 않고, 반응형 레이아웃, 프리미엄 UI/UX 디자인, 실시간 데이터 동기화 등 실무 수준의 품질을 갖춘 완성도 높은 서비스로 발전시켰습니다.</t>
-  </si>
-  <si>
     <t>구현기능</t>
+  </si>
+  <si>
+    <t>개발계획</t>
+  </si>
+  <si>
+    <t>사용기술 및 개발환경</t>
+  </si>
+  <si>
+    <t>프로젝트 주제
+"현대적 소셜 미디어의 핵심 사용자 경험을 집약한 모바일 퍼스트 SNS 플랫폼"
+본 프로젝트는 인스타그램, 트위터와 같은 글로벌 SNS의 핵심 기능을 벤치마킹하여, 사용자 간의 실시간 소통과 위치 기반 정보 공유를 극대화한 웹 애플리케이션입니다.
+2. 개발 목적 및 배경
+모바일 최적화 경험 구현: '모바일 퍼스트' 원칙에 따라 다양한 디바이스 환경에서 끊김 없는 UI/UX를 제공하는 데 집중했습니다.
+실시간 데이터 인터랙션: Firebase의 Realtime DB와 Firestore를 활용하여 채팅, 좋아요, 알림 등 실시간 응답성이 필요한 기능을 구현하며 서버리스 아키텍처의 효율성을 경험했습니다.
+위치 기반 기술 접목: Google Maps API를 연동하여 단순히 글을 올리는 것을 넘어, '장소'를 매개로 사용자들이 소통할 수 있는 차별화된 기능을 구현했습니다.
+최신 웹 기술 스택 숙달: Next.js의 SSR/CSR 하이브리드 렌더링을 활용하여 검색 엔진 최적화(SEO)와 빠른 사용자 전환 성능을 동시에 확보하고자 했습니다.습니다. 단순 기능 구현에 그치지 않고, 반응형 레이아웃, 프리미엄 UI/UX 디자인, 실시간 데이터 동기화 등 실무 수준의 품질을 갖춘 완성도 높은 서비스로 발전시켰습니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>소셜 피드 시스템 (Feed)
@@ -87,47 +95,41 @@
 알림 시스템 (Notifications)
 - 좋아요, 댓글, 팔로우 실시간 알림
 - 읽음/안읽음 상태 관리</t>
-  </si>
-  <si>
-    <t>개발계획</t>
-  </si>
-  <si>
-    <t>1주차: 프로젝트 기반 구축 및 인증 시스템
-- Next.js + TypeScript 프로젝트 초기 설정 및 Firebase 연동
-- Firebase Auth 기반 회원가입/로그인 시스템 구축
-- 공통 레이아웃 (SideNav, BottomNav, RightPanel) 구현
-2주차: 소셜 피드 및 스토리 핵심 기능 개발
-- 이미지 업로드 기반 게시물 CRUD 로직 구현
-- 좋아요, 댓글, 북마크 인터랙션 개발
-- 24시간 만료 스토리 시스템 설계 및 구현
-3주차: 실시간 채팅 및 지도 기능 개발
-- Firebase Realtime Database 기반 1:1 및 그룹 채팅 구현
-- Google Maps API 연동 Discovery 페이지 개발
-- 그룹 정산 시스템 구축
-4주차: UI/UX 고도화 및 최종 리팩토링
-- 반응형 레이아웃 (모바일/태블릿/PC) 최적화
-- 프리미엄 UI 디자인 적용 (글래스모피즘, 마이크로 애니메이션)
-- 전체 시스템 테스트 및 성능 최적화</t>
-  </si>
-  <si>
-    <t>사용기술 및 개발환경</t>
-  </si>
-  <si>
-    <t>- 개발환경 : Windows 11
-- 개발도구 : VS Code, Git
-- 개발언어 및 프레임워크 : TypeScript, Next.js 16 (React 19)
-- 스타일링 : TailwindCSS 4
-- 백엔드/DB : Firebase (Firestore, Auth, Realtime DB, Storage)
-- API : Google Maps API
-- 패키지 매니저 : npm
-- 배포 : Vercel (예정)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 효율적인 서버리스(Serverless) 아키텍처 활용
+Firebase의 전방위 활용: 백엔드 서버를 직접 구축하는 대신 Firebase Auth(인증), Firestore(DB), Storage(이미지)를 즉시 도입하여 인프라 구축 시간을 80% 이상 단축했습니다.
+Realtime DB의 선택: 복잡한 소켓 설정 없이 Firebase Realtime Database를 사용하여 실시간 채팅 기능을 단 며칠 만에 안정적으로 구현했습니다.
+2. Next.js 기반의 생산성 극대화
+컴포넌트 기반 개발: SideNav, BottomNav 등을 공통 레이아웃으로 분리하여 화면 전환 속도를 높이고 코드 재사용성을 극대화했습니다.
+TypeScript의 안정성: 타입 정의를 통해 개발 단계에서 버그를 사전에 차단함으로써 디버깅 시간을 대폭 줄였습니다.
+3. 모듈형 기능 구현 (Agile Approach)
+도메인별 집중 개발: 1주 차에는 '인증과 뼈대', 2주 차에는 **'콘텐츠와 소통'**이라는 명확한 목표를 세우고 병렬적으로 기능을 붙여 나갔습니다.
+API 중심 설계: Google Maps나 Firebase 같은 강력한 외부 API를 적극적으로 연동하여 핵심 비즈니스 로직(정산, 스토리 만료 등) 개발에만 집중할 수 있었습니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>개발 환경 : Windows 11
+개발 도구 : VS Code, Git
+언어 및 프레임워크 : TypeScript, Next.js 16 (React 19)
+스타일링 : TailwindCSS 4
+백엔드/DB : Firebase (Firestore, Auth, Realtime DB, Storage)
+사용 API : Google Maps API
+패키지 매니저 : npm
+배포 플랫폼 : Vercel (https://sns-khaki-psi.vercel.app/login)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SNS 프로젝트 (모바일 반응형 소셜 네트워크 서비스)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -162,6 +164,20 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -177,7 +193,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -200,37 +216,155 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -533,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I12"/>
+  <dimension ref="B2:I13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -541,156 +675,167 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B5" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="11" t="s">
+      <c r="C5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="11" t="s">
+      <c r="C6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="10" t="s">
+      <c r="C7" s="23">
+        <v>46108</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="G7" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="1" t="s">
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+    </row>
+    <row r="8" spans="2:9" ht="219.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="C8" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+    </row>
+    <row r="9" spans="2:9" ht="200.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" spans="2:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="9" t="s">
+      <c r="C9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" spans="2:9" ht="200.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="10"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+    </row>
+    <row r="11" spans="2:9" ht="200.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C11" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="19"/>
+    </row>
+    <row r="12" spans="2:9" s="2" customFormat="1" ht="69.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="16"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="22"/>
+    </row>
+    <row r="13" spans="2:9" ht="129.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" spans="2:9" ht="200.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-    </row>
-    <row r="10" spans="2:9" ht="200.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="8"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" spans="2:9" ht="200.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="C13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" spans="2:9" ht="129.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="C12:I12"/>
-    <mergeCell ref="C6:I6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="C11:I11"/>
+  <mergeCells count="12">
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:I12"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="C9:I10"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="C8:I8"/>
     <mergeCell ref="C4:I4"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="C5:I5"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
